--- a/DATA/setting.xlsx
+++ b/DATA/setting.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cuilleret\Documents\gamsdir\projdir\Model_Dahbsim_06_03_2026_generic- calib2\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cuilleret\Documents\gamsdir\projdir\Model_Dahbsim_20_04_2026\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3255E624-75CD-4439-8B69-4172A238BF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF07A28-F378-40A1-9C8A-798729013AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{6805678B-7C95-42D4-AC07-B8283DFB4E6B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6805678B-7C95-42D4-AC07-B8283DFB4E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="setting" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
     <t>BIOPHcalib</t>
   </si>
   <si>
-    <t>tizi</t>
+    <t>luxor</t>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -826,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -846,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
